--- a/outputs/daily/hr_rankings_2026-10-17_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-17_remaining.xlsx
@@ -735,32 +735,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -768,23 +768,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Shawn Armstrong</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>542888</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>52.8</v>
+        <v>51.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,30 +786,30 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>61.9</v>
+        <v>53.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>32</v>
+        <v>41.2</v>
       </c>
       <c r="R2" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>94.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U2" t="n">
-        <v>37.8</v>
+        <v>34.9</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -841,18 +829,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -874,7 +866,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -884,124 +876,92 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2549</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>35.04</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>88.35</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.3695</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.1577</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>0.1874</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1015,12 +975,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1035,36 +995,36 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1078,30 +1038,30 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.9</v>
+        <v>61.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>32</v>
+        <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1111,7 +1071,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1121,15 +1081,19 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1149,12 +1113,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1164,124 +1128,116 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.2549</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1295,12 +1251,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1315,36 +1271,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>50.3</v>
+        <v>46.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1358,30 +1302,30 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>53.3</v>
+        <v>35.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R4" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U4" t="n">
-        <v>34.9</v>
+        <v>56.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1391,7 +1335,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1401,18 +1345,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1429,27 +1377,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1459,109 +1407,77 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>101.3425</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>72.74</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1874</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1575,56 +1491,56 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.3</v>
+        <v>44.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,30 +1554,30 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>35.1</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>34.3</v>
+        <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>96.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>56.2</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1671,7 +1587,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1681,18 +1597,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1709,27 +1629,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1739,109 +1659,101 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.3425</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1855,56 +1767,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Victor Mesa Jr.</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Shawn Armstrong</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>542888</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>47.6</v>
+        <v>43.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1918,30 +1818,30 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>43.6</v>
+        <v>25.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>40.2</v>
       </c>
       <c r="R6" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>76.2</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U6" t="n">
-        <v>54.9</v>
+        <v>23.4</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1951,7 +1851,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1961,18 +1861,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1994,22 +1898,22 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2019,109 +1923,77 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>35.04</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>88.35</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0.3695</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0.1577</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>0.1591</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2155,12 +2027,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2168,23 +2040,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>45</v>
+        <v>43.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2198,30 +2058,30 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P7" t="n">
         <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R7" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>86.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U7" t="n">
         <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -2241,18 +2101,22 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2289,7 +2153,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2362,46 +2226,14 @@
           <t>0.1803</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2420,7 +2252,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yandy Díaz</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2435,12 +2267,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2450,21 +2282,21 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.8</v>
+        <v>43.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2478,30 +2310,30 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
         <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>21.5</v>
       </c>
       <c r="R8" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>93.2</v>
+        <v>88.7</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U8" t="n">
         <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -2521,15 +2353,19 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2569,7 +2405,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2644,44 +2480,36 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2695,12 +2523,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>José Ramírez</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2715,36 +2543,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>43.2</v>
+        <v>42</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2758,30 +2574,30 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>25.8</v>
+        <v>32.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.5</v>
+        <v>40.2</v>
       </c>
       <c r="R9" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>59.8</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>23.4</v>
+        <v>48.7</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -2791,7 +2607,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2801,18 +2617,22 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2829,27 +2649,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2859,109 +2679,77 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1591</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>0.1212</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2975,56 +2763,56 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>41.6</v>
+        <v>41</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3038,30 +2826,30 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.4</v>
+        <v>43.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>32.5</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>64.3</v>
+        <v>71.7</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>48.7</v>
+        <v>54.9</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -3071,7 +2859,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3081,15 +2869,19 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3109,27 +2901,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3139,109 +2931,101 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3275,12 +3059,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3288,23 +3072,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>38.6</v>
+        <v>37</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3318,30 +3090,30 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P11" t="n">
         <v>20.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>76.2</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U11" t="n">
         <v>12</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -3361,18 +3133,22 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3409,7 +3185,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3482,46 +3258,14 @@
           <t>0.163</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3555,12 +3299,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3568,23 +3312,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>36.6</v>
+        <v>35</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3598,30 +3330,30 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
         <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R12" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>93.2</v>
+        <v>88.7</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U12" t="n">
         <v>43.1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -3641,18 +3373,22 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3689,7 +3425,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3762,46 +3498,14 @@
           <t>0.0775</t>
         </is>
       </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3815,56 +3519,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Shawn Armstrong</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>542888</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>35.5</v>
+        <v>34.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3878,30 +3570,30 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>13.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>40.2</v>
       </c>
       <c r="R13" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>86.40000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5</v>
+        <v>72.7</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -3911,7 +3603,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3921,18 +3613,22 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3949,27 +3645,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3979,109 +3675,77 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>35.04</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>88.35</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0.3695</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0.1577</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4095,12 +3759,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4115,36 +3779,36 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34.2</v>
+        <v>31.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4158,30 +3822,30 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.2</v>
+        <v>10.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>32</v>
+        <v>21.5</v>
       </c>
       <c r="R14" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>96.59999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U14" t="n">
-        <v>15.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -4191,7 +3855,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4201,15 +3865,19 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4229,27 +3897,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4259,109 +3927,101 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4375,12 +4035,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4395,36 +4055,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>33.9</v>
+        <v>30.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4438,30 +4086,30 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>13.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>32.5</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>72.7</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -4471,7 +4119,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4481,18 +4129,22 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4509,27 +4161,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4539,109 +4191,77 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1287</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>0.0707</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4655,12 +4275,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4675,36 +4295,36 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>33.2</v>
+        <v>28.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4718,30 +4338,30 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>32</v>
+        <v>21.5</v>
       </c>
       <c r="R16" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>64.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -4751,7 +4371,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4761,15 +4381,19 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4789,27 +4413,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4819,109 +4443,101 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4935,12 +4551,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4955,36 +4571,36 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>33.2</v>
+        <v>27.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4998,30 +4614,30 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>32</v>
+        <v>21.5</v>
       </c>
       <c r="R17" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>52.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -5031,7 +4647,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5041,15 +4657,19 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5069,12 +4689,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5084,12 +4704,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5099,109 +4719,101 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5215,32 +4827,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5250,21 +4862,21 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32</v>
+        <v>26.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5278,30 +4890,30 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>7.1</v>
+        <v>15.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>34.3</v>
+        <v>21.5</v>
       </c>
       <c r="R18" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>52.4</v>
+        <v>47.9</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>38.3</v>
+        <v>19.5</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -5321,15 +4933,19 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5349,12 +4965,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5364,12 +4980,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5379,109 +4995,101 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5515,12 +5123,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5530,21 +5138,21 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.8</v>
+        <v>24.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5558,20 +5166,20 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>31.5</v>
+        <v>20.1</v>
       </c>
       <c r="R19" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>44.8</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5581,7 +5189,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -5601,15 +5209,19 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5649,7 +5261,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5724,44 +5336,36 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6101,32 +5705,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6134,23 +5738,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Shawn Armstrong</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>542888</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>52.8</v>
+        <v>51.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6164,30 +5756,30 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>61.9</v>
+        <v>53.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>32</v>
+        <v>41.2</v>
       </c>
       <c r="R2" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>94.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U2" t="n">
-        <v>37.8</v>
+        <v>34.9</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -6207,18 +5799,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -6240,7 +5836,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -6250,124 +5846,92 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2549</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>35.04</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>88.35</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.3695</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.1577</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>0.1874</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6381,12 +5945,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6401,36 +5965,36 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6444,30 +6008,30 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.9</v>
+        <v>61.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>32</v>
+        <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -6477,7 +6041,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -6487,15 +6051,19 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6515,12 +6083,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -6530,124 +6098,116 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.2549</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6661,12 +6221,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>800050</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Chase DeLauter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6681,36 +6241,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>50.3</v>
+        <v>46.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6724,30 +6272,30 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>53.3</v>
+        <v>35.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R4" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U4" t="n">
-        <v>34.9</v>
+        <v>56.2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -6757,7 +6305,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -6767,18 +6315,22 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -6795,27 +6347,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -6825,109 +6377,77 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>101.3425</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>72.74</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1874</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6941,56 +6461,56 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>800050</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chase DeLauter</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.3</v>
+        <v>44.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7004,30 +6524,30 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>35.1</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>34.3</v>
+        <v>21.5</v>
       </c>
       <c r="R5" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>96.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>56.2</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -7037,7 +6557,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -7047,18 +6567,22 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -7075,27 +6599,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -7105,109 +6629,101 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.3425</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7221,56 +6737,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Victor Mesa Jr.</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Shawn Armstrong</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>542888</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>47.6</v>
+        <v>43.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7284,30 +6788,30 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>43.6</v>
+        <v>25.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>40.2</v>
       </c>
       <c r="R6" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>76.2</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U6" t="n">
-        <v>54.9</v>
+        <v>23.4</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -7317,7 +6821,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -7327,18 +6831,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -7360,22 +6868,22 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7385,109 +6893,77 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.2134</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>35.04</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>88.35</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0.3695</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0.1577</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>0.1591</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7521,12 +6997,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7534,23 +7010,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>45</v>
+        <v>43.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7564,30 +7028,30 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P7" t="n">
         <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R7" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>86.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U7" t="n">
         <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -7607,18 +7071,22 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7655,7 +7123,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7728,46 +7196,14 @@
           <t>0.1803</t>
         </is>
       </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7786,7 +7222,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yandy Díaz</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7801,12 +7237,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7816,21 +7252,21 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.8</v>
+        <v>43.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7844,30 +7280,30 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
         <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>32</v>
+        <v>21.5</v>
       </c>
       <c r="R8" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>93.2</v>
+        <v>88.7</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U8" t="n">
         <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -7887,15 +7323,19 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7935,7 +7375,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -8010,44 +7450,36 @@
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8061,12 +7493,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>José Ramírez</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8081,36 +7513,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>43.2</v>
+        <v>42</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8124,30 +7544,30 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>25.8</v>
+        <v>32.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.5</v>
+        <v>40.2</v>
       </c>
       <c r="R9" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>59.8</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
       </c>
       <c r="U9" t="n">
-        <v>23.4</v>
+        <v>48.7</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -8157,7 +7577,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -8167,18 +7587,22 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -8195,27 +7619,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8225,109 +7649,77 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1591</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>0.1212</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8341,56 +7733,56 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>41.6</v>
+        <v>41</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8404,30 +7796,30 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.4</v>
+        <v>43.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>32.5</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>64.3</v>
+        <v>71.7</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>48.7</v>
+        <v>54.9</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -8437,7 +7829,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -8447,15 +7839,19 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8475,27 +7871,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8505,109 +7901,101 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8641,12 +8029,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8654,23 +8042,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>38.6</v>
+        <v>37</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8684,30 +8060,30 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P11" t="n">
         <v>20.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>76.2</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U11" t="n">
         <v>12</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -8727,18 +8103,22 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8775,7 +8155,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8848,46 +8228,14 @@
           <t>0.163</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8921,12 +8269,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8934,23 +8282,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>36.6</v>
+        <v>35</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8964,30 +8300,30 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P12" t="n">
         <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R12" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>93.2</v>
+        <v>88.7</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U12" t="n">
         <v>43.1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -9007,18 +8343,22 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -9055,7 +8395,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -9128,46 +8468,14 @@
           <t>0.0775</t>
         </is>
       </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9181,56 +8489,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Shawn Armstrong</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>542888</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>35.5</v>
+        <v>34.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9244,30 +8540,30 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>13.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>40.2</v>
       </c>
       <c r="R13" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>86.40000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5</v>
+        <v>72.7</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -9277,7 +8573,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -9287,18 +8583,22 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -9315,27 +8615,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9345,109 +8645,77 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>35.04</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>88.35</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0.3695</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0.1577</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9461,12 +8729,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9481,36 +8749,36 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34.2</v>
+        <v>31.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9524,30 +8792,30 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.2</v>
+        <v>10.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>32</v>
+        <v>21.5</v>
       </c>
       <c r="R14" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>96.59999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U14" t="n">
-        <v>15.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -9557,7 +8825,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -9567,15 +8835,19 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9595,27 +8867,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9625,109 +8897,101 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9741,12 +9005,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9761,36 +9025,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Nick Martinez</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>607259</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>33.9</v>
+        <v>30.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9804,30 +9056,30 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>13.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>32.5</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>72.7</v>
+        <v>38.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -9837,7 +9089,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -9847,18 +9099,22 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9875,27 +9131,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9905,109 +9161,77 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1287</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>6.86</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>33.38</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>87.39</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0.4114</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0.1502</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>0.0707</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10021,12 +9245,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10041,36 +9265,36 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>33.2</v>
+        <v>28.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10084,30 +9308,30 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>32</v>
+        <v>21.5</v>
       </c>
       <c r="R16" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>64.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -10117,7 +9341,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -10127,15 +9351,19 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10155,27 +9383,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10185,109 +9413,101 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10301,12 +9521,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10321,36 +9541,36 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>33.2</v>
+        <v>27.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10364,30 +9584,30 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>32</v>
+        <v>21.5</v>
       </c>
       <c r="R17" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>52.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -10397,7 +9617,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -10407,15 +9627,19 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10435,12 +9659,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10450,12 +9674,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10465,109 +9689,101 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10581,32 +9797,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10616,21 +9832,21 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>32</v>
+        <v>26.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10644,30 +9860,30 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>7.1</v>
+        <v>15.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>34.3</v>
+        <v>21.5</v>
       </c>
       <c r="R18" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>52.4</v>
+        <v>47.9</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>38.3</v>
+        <v>19.5</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -10687,15 +9903,19 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10715,12 +9935,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10730,12 +9950,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10745,109 +9965,101 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10881,12 +10093,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-18T00:08:00Z</t>
+          <t>2026-10-18T21:08:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10896,21 +10108,21 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.8</v>
+        <v>24.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10924,20 +10136,20 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>31.5</v>
+        <v>20.1</v>
       </c>
       <c r="R19" t="n">
-        <v>33.1</v>
+        <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>44.8</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10947,7 +10159,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -10967,15 +10179,19 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11015,7 +10231,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -11090,44 +10306,36 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>
